--- a/test-files/gene-name-modifications/duplicate-gene-side-and-top-input.xlsx
+++ b/test-files/gene-name-modifications/duplicate-gene-side-and-top-input.xlsx
@@ -1,71 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25915"/>
-  <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14160" tabRatio="759"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="false" showInkAnnotation="false"/>
   <sheets>
-    <sheet name="network" sheetId="14" r:id="rId1"/>
+    <sheet name="network" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>duplicate</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,77 +61,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="31">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="31">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="26" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="28" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="30" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="25" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="27" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="29" builtinId="8" hidden="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -480,39 +396,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>A</v>
+      </c>
+      <c r="C1" t="str">
+        <v>duplicate</v>
+      </c>
+      <c r="D1" t="str">
+        <v>duplicate</v>
+      </c>
+      <c r="E1" t="str">
+        <v>B</v>
+      </c>
+      <c r="F1" t="str">
+        <v>C</v>
+      </c>
+      <c r="G1" t="str">
+        <v>D</v>
+      </c>
+      <c r="H1" t="str">
+        <v>E</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -536,9 +451,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>1</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>duplicate</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -562,9 +477,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>1</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>duplicate</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -588,9 +503,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>3</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>B</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -614,9 +529,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>5</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>C</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -640,9 +555,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>6</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>D</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -666,9 +581,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>4</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>E</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -693,12 +608,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
+  </ignoredErrors>
 </worksheet>
 </file>